--- a/data/transactions/أذونات الإضافة لشهر 6.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEE282A-B314-40FB-91F8-B5A9C6B6F4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2302EB-8280-4D5D-A011-368C7DEC7BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1866,9 +1866,6 @@
     <t>10406026</t>
   </si>
   <si>
-    <t>11404002</t>
-  </si>
-  <si>
     <t>11404008</t>
   </si>
   <si>
@@ -2428,6 +2425,9 @@
   </si>
   <si>
     <t>جالون كولة شعلة</t>
+  </si>
+  <si>
+    <t>11404012</t>
   </si>
 </sst>
 </file>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B89" s="14"/>
       <c r="C89" s="15" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>15</v>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="J90" s="3"/>
       <c r="K90" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L90" s="3">
         <v>6388</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="J91" s="3"/>
       <c r="K91" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L91" s="3">
         <v>6388</v>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="J158" s="3"/>
       <c r="K158" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L158" s="3">
         <v>6403</v>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="J159" s="3"/>
       <c r="K159" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L159" s="3">
         <v>6403</v>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="J160" s="3"/>
       <c r="K160" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L160" s="3">
         <v>6403</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="J182" s="3"/>
       <c r="K182" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L182" s="3">
         <v>6409</v>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="J183" s="3"/>
       <c r="K183" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L183" s="3">
         <v>6409</v>
@@ -10171,10 +10171,10 @@
         <v>184</v>
       </c>
       <c r="B188" s="25" t="s">
-        <v>612</v>
+        <v>799</v>
       </c>
       <c r="C188" s="23" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D188" s="28" t="s">
         <v>77</v>
@@ -10210,10 +10210,10 @@
         <v>185</v>
       </c>
       <c r="B189" s="25" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C189" s="23" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D189" s="28" t="s">
         <v>77</v>
@@ -10245,10 +10245,10 @@
         <v>186</v>
       </c>
       <c r="B190" s="25" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C190" s="23" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D190" s="28" t="s">
         <v>77</v>
@@ -10280,10 +10280,10 @@
         <v>187</v>
       </c>
       <c r="B191" s="25" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C191" s="23" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D191" s="28" t="s">
         <v>77</v>
@@ -10315,10 +10315,10 @@
         <v>188</v>
       </c>
       <c r="B192" s="25" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C192" s="23" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D192" s="28" t="s">
         <v>77</v>
@@ -10350,7 +10350,7 @@
         <v>189</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C193" s="3" t="s">
         <v>212</v>
@@ -10389,7 +10389,7 @@
         <v>190</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>214</v>
@@ -10428,7 +10428,7 @@
         <v>191</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>215</v>
@@ -10467,10 +10467,10 @@
         <v>192</v>
       </c>
       <c r="B196" s="12" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D196" s="3" t="s">
         <v>15</v>
@@ -10509,7 +10509,7 @@
         <v>443</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>15</v>
@@ -10545,7 +10545,7 @@
         <v>194</v>
       </c>
       <c r="B198" s="11" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>217</v>
@@ -10584,7 +10584,7 @@
         <v>195</v>
       </c>
       <c r="B199" s="12" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C199" s="3" t="s">
         <v>218</v>
@@ -10623,7 +10623,7 @@
         <v>196</v>
       </c>
       <c r="B200" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>219</v>
@@ -10662,7 +10662,7 @@
         <v>197</v>
       </c>
       <c r="B201" s="12" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C201" s="3" t="s">
         <v>220</v>
@@ -10701,7 +10701,7 @@
         <v>198</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>221</v>
@@ -10740,7 +10740,7 @@
         <v>199</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>222</v>
@@ -10779,7 +10779,7 @@
         <v>200</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>223</v>
@@ -10818,7 +10818,7 @@
         <v>201</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C205" s="3" t="s">
         <v>228</v>
@@ -10857,7 +10857,7 @@
         <v>202</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C206" s="3" t="s">
         <v>224</v>
@@ -10896,7 +10896,7 @@
         <v>203</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C207" s="3" t="s">
         <v>225</v>
@@ -10935,7 +10935,7 @@
         <v>205</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C208" s="3" t="s">
         <v>226</v>
@@ -10974,7 +10974,7 @@
         <v>207</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>227</v>
@@ -11013,7 +11013,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>230</v>
@@ -11052,7 +11052,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>231</v>
@@ -11091,7 +11091,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>232</v>
@@ -11130,7 +11130,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>233</v>
@@ -11169,7 +11169,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C214" s="3" t="s">
         <v>234</v>
@@ -11208,7 +11208,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C215" s="3" t="s">
         <v>235</v>
@@ -11247,7 +11247,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>236</v>
@@ -11286,7 +11286,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>237</v>
@@ -11364,7 +11364,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C219" s="3" t="s">
         <v>239</v>
@@ -11442,7 +11442,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C221" s="3" t="s">
         <v>241</v>
@@ -11481,7 +11481,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C222" s="3" t="s">
         <v>242</v>
@@ -11520,7 +11520,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C223" s="3" t="s">
         <v>243</v>
@@ -11559,7 +11559,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>244</v>
@@ -11598,7 +11598,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>245</v>
@@ -11637,7 +11637,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>246</v>
@@ -11676,7 +11676,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C227" s="3" t="s">
         <v>247</v>
@@ -11715,7 +11715,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C228" s="3" t="s">
         <v>248</v>
@@ -11754,7 +11754,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C229" s="3" t="s">
         <v>249</v>
@@ -11793,7 +11793,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>250</v>
@@ -11869,7 +11869,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C232" s="3" t="s">
         <v>252</v>
@@ -11947,7 +11947,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C234" s="3" t="s">
         <v>254</v>
@@ -11986,7 +11986,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>255</v>
@@ -12025,7 +12025,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>256</v>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="J237" s="3"/>
       <c r="K237" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L237" s="3">
         <v>6420</v>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="J238" s="3"/>
       <c r="K238" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L238" s="3">
         <v>6420</v>
@@ -12167,7 +12167,7 @@
       </c>
       <c r="J239" s="3"/>
       <c r="K239" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L239" s="3">
         <v>6420</v>
@@ -12181,7 +12181,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>260</v>
@@ -12220,7 +12220,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>262</v>
@@ -12259,7 +12259,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>263</v>
@@ -12298,7 +12298,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>264</v>
@@ -12337,7 +12337,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>265</v>
@@ -12376,10 +12376,10 @@
         <v>245</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>15</v>
@@ -12415,7 +12415,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>266</v>
@@ -12454,7 +12454,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>267</v>
@@ -12493,7 +12493,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>268</v>
@@ -12532,7 +12532,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>269</v>
@@ -12571,7 +12571,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>270</v>
@@ -12610,10 +12610,10 @@
         <v>251</v>
       </c>
       <c r="B251" s="12" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D251" s="3" t="s">
         <v>15</v>
@@ -12687,7 +12687,7 @@
       </c>
       <c r="B253" s="26"/>
       <c r="C253" s="23" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D253" s="23" t="s">
         <v>15</v>
@@ -12799,7 +12799,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="6" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>261</v>
@@ -12838,7 +12838,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>273</v>
@@ -12877,7 +12877,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>274</v>
@@ -12916,7 +12916,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>275</v>
@@ -12992,7 +12992,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>277</v>
@@ -13031,7 +13031,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>278</v>
@@ -13070,7 +13070,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C263" s="3" t="s">
         <v>279</v>
@@ -13109,7 +13109,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C264" s="3" t="s">
         <v>281</v>
@@ -13148,7 +13148,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>282</v>
@@ -13187,7 +13187,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C266" s="3" t="s">
         <v>283</v>
@@ -13226,7 +13226,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="12" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C267" s="3" t="s">
         <v>285</v>
@@ -13265,7 +13265,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C268" s="3" t="s">
         <v>287</v>
@@ -13304,7 +13304,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C269" s="3" t="s">
         <v>288</v>
@@ -13343,7 +13343,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C270" s="3" t="s">
         <v>289</v>
@@ -13382,7 +13382,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C271" s="3" t="s">
         <v>290</v>
@@ -13421,7 +13421,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C272" s="3" t="s">
         <v>291</v>
@@ -13460,7 +13460,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C273" s="3" t="s">
         <v>292</v>
@@ -13499,7 +13499,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C274" s="3" t="s">
         <v>293</v>
@@ -13577,7 +13577,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>295</v>
@@ -13616,7 +13616,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C277" s="3" t="s">
         <v>296</v>
@@ -13655,7 +13655,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C278" s="3" t="s">
         <v>297</v>
@@ -13694,7 +13694,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C279" s="3" t="s">
         <v>298</v>
@@ -13733,7 +13733,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>299</v>
@@ -13772,7 +13772,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>300</v>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="J282" s="3"/>
       <c r="K282" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L282" s="3">
         <v>6436</v>
@@ -13875,7 +13875,7 @@
       </c>
       <c r="J283" s="3"/>
       <c r="K283" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L283" s="3">
         <v>6436</v>
@@ -13914,7 +13914,7 @@
       </c>
       <c r="J284" s="3"/>
       <c r="K284" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L284" s="3">
         <v>6436</v>
@@ -13970,7 +13970,7 @@
         <v>532</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D286" s="3" t="s">
         <v>15</v>
@@ -14084,7 +14084,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C289" s="3" t="s">
         <v>303</v>
@@ -14123,7 +14123,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C290" s="3" t="s">
         <v>304</v>
@@ -14162,7 +14162,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="6" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C291" s="3" t="s">
         <v>305</v>
@@ -14201,7 +14201,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="6" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C292" s="3" t="s">
         <v>306</v>
@@ -14240,7 +14240,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C293" s="3" t="s">
         <v>307</v>
@@ -14279,7 +14279,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="6" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C294" s="3" t="s">
         <v>308</v>
@@ -14318,7 +14318,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C295" s="3" t="s">
         <v>309</v>
@@ -14435,7 +14435,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="11" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C298" s="3" t="s">
         <v>310</v>
@@ -14474,7 +14474,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="12" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C299" s="3" t="s">
         <v>311</v>
@@ -14513,7 +14513,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="12" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C300" s="3" t="s">
         <v>312</v>
@@ -14552,7 +14552,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="12" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C301" s="3" t="s">
         <v>320</v>
@@ -14591,7 +14591,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="12" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C302" s="3" t="s">
         <v>313</v>
@@ -14669,7 +14669,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="12" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C304" s="3" t="s">
         <v>315</v>
@@ -14708,7 +14708,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="11" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C305" s="3" t="s">
         <v>316</v>
@@ -14747,7 +14747,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="12" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C306" s="3" t="s">
         <v>317</v>
@@ -14825,7 +14825,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="11" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C308" s="3" t="s">
         <v>319</v>
@@ -14903,7 +14903,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="11" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C310" s="3" t="s">
         <v>322</v>
@@ -14942,7 +14942,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="11" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C311" s="3" t="s">
         <v>323</v>
@@ -14981,7 +14981,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="11" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>324</v>
@@ -15020,7 +15020,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="11" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C313" s="3" t="s">
         <v>325</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="J314" s="23"/>
       <c r="K314" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L314" s="23">
         <v>6441</v>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="J315" s="23"/>
       <c r="K315" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L315" s="23">
         <v>6441</v>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="J316" s="23"/>
       <c r="K316" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L316" s="23">
         <v>6441</v>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="J317" s="23"/>
       <c r="K317" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L317" s="23">
         <v>6441</v>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="J318" s="23"/>
       <c r="K318" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L318" s="23">
         <v>6441</v>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="J319" s="23"/>
       <c r="K319" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L319" s="23">
         <v>6441</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="J320" s="23"/>
       <c r="K320" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L320" s="23">
         <v>6441</v>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="J321" s="23"/>
       <c r="K321" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L321" s="23">
         <v>6441</v>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="J322" s="23"/>
       <c r="K322" s="23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L322" s="23">
         <v>6441</v>
@@ -15431,7 +15431,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C324" s="3" t="s">
         <v>336</v>
@@ -15470,7 +15470,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C325" s="3" t="s">
         <v>337</v>
@@ -15509,7 +15509,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="6" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C326" s="3" t="s">
         <v>338</v>
@@ -15548,7 +15548,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="6" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C327" s="3" t="s">
         <v>339</v>
@@ -15587,7 +15587,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="6" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C328" s="3" t="s">
         <v>340</v>
@@ -15626,7 +15626,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="6" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C329" s="3" t="s">
         <v>341</v>
@@ -15665,7 +15665,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="6" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C330" s="3" t="s">
         <v>342</v>
@@ -15704,7 +15704,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="6" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C331" s="3" t="s">
         <v>343</v>
@@ -15743,7 +15743,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C332" s="3" t="s">
         <v>344</v>
@@ -15782,7 +15782,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C333" s="3" t="s">
         <v>345</v>
@@ -15821,7 +15821,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="6" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C334" s="3" t="s">
         <v>346</v>
@@ -15860,7 +15860,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C335" s="3" t="s">
         <v>347</v>
@@ -15899,7 +15899,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C336" s="3" t="s">
         <v>348</v>
@@ -15938,7 +15938,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C337" s="3" t="s">
         <v>350</v>
@@ -15977,7 +15977,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C338" s="3" t="s">
         <v>351</v>
@@ -16016,7 +16016,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="12" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C339" s="3" t="s">
         <v>352</v>
@@ -16055,7 +16055,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C340" s="3" t="s">
         <v>353</v>
@@ -16094,7 +16094,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="12" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C341" s="3" t="s">
         <v>354</v>
@@ -16133,7 +16133,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="12" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C342" s="3" t="s">
         <v>355</v>
@@ -16172,7 +16172,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="13" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C343" s="3" t="s">
         <v>356</v>
@@ -16211,7 +16211,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="12" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C344" s="3" t="s">
         <v>357</v>
@@ -16328,7 +16328,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="12" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C347" s="3" t="s">
         <v>358</v>
@@ -16406,7 +16406,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C349" s="3" t="s">
         <v>359</v>
@@ -16445,7 +16445,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C350" s="3" t="s">
         <v>360</v>
@@ -16484,7 +16484,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C351" s="3" t="s">
         <v>361</v>
@@ -16523,7 +16523,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C352" s="3" t="s">
         <v>362</v>
@@ -16562,7 +16562,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="12" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C353" s="3" t="s">
         <v>363</v>
@@ -16601,7 +16601,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="12" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C354" s="3" t="s">
         <v>364</v>
@@ -16640,7 +16640,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="13" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C355" s="3" t="s">
         <v>365</v>
@@ -16679,7 +16679,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="12" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C356" s="3" t="s">
         <v>366</v>
@@ -16718,7 +16718,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C357" s="3" t="s">
         <v>367</v>
@@ -16757,7 +16757,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C358" s="3" t="s">
         <v>369</v>
@@ -16796,7 +16796,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C359" s="3" t="s">
         <v>368</v>
@@ -16913,7 +16913,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="6" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C362" s="3" t="s">
         <v>373</v>
@@ -16991,7 +16991,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C364" s="3" t="s">
         <v>374</v>
@@ -17030,7 +17030,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C365" s="3" t="s">
         <v>375</v>
@@ -17069,7 +17069,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C366" s="3" t="s">
         <v>376</v>
@@ -17108,7 +17108,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="6" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C367" s="3" t="s">
         <v>377</v>
@@ -17225,10 +17225,10 @@
         <v>370</v>
       </c>
       <c r="B370" s="6" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D370" s="3" t="s">
         <v>15</v>
@@ -17303,7 +17303,7 @@
         <v>376</v>
       </c>
       <c r="B372" s="12" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C372" s="3" t="s">
         <v>382</v>
@@ -17342,10 +17342,10 @@
         <v>377</v>
       </c>
       <c r="B373" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="C373" s="3" t="s">
         <v>755</v>
-      </c>
-      <c r="C373" s="3" t="s">
-        <v>756</v>
       </c>
       <c r="D373" s="3" t="s">
         <v>15</v>
@@ -17381,7 +17381,7 @@
         <v>378</v>
       </c>
       <c r="B374" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C374" s="3" t="s">
         <v>383</v>
@@ -17420,7 +17420,7 @@
         <v>379</v>
       </c>
       <c r="B375" s="12" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C375" s="3" t="s">
         <v>384</v>
@@ -17498,7 +17498,7 @@
         <v>381</v>
       </c>
       <c r="B377" s="12" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C377" s="3" t="s">
         <v>385</v>
@@ -17537,7 +17537,7 @@
         <v>382</v>
       </c>
       <c r="B378" s="12" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C378" s="3" t="s">
         <v>386</v>
@@ -17576,7 +17576,7 @@
         <v>383</v>
       </c>
       <c r="B379" s="12" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C379" s="3" t="s">
         <v>387</v>
@@ -17615,7 +17615,7 @@
         <v>384</v>
       </c>
       <c r="B380" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C380" s="3" t="s">
         <v>388</v>
@@ -17654,7 +17654,7 @@
         <v>385</v>
       </c>
       <c r="B381" s="12" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C381" s="3" t="s">
         <v>389</v>
@@ -17693,7 +17693,7 @@
         <v>386</v>
       </c>
       <c r="B382" s="12" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C382" s="3" t="s">
         <v>390</v>
@@ -17732,7 +17732,7 @@
         <v>387</v>
       </c>
       <c r="B383" s="12" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C383" s="3" t="s">
         <v>391</v>
@@ -17771,7 +17771,7 @@
         <v>388</v>
       </c>
       <c r="B384" s="12" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C384" s="3" t="s">
         <v>393</v>
@@ -17810,7 +17810,7 @@
         <v>389</v>
       </c>
       <c r="B385" s="12" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C385" s="3" t="s">
         <v>394</v>
@@ -17849,7 +17849,7 @@
         <v>391</v>
       </c>
       <c r="B386" s="12" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C386" s="3" t="s">
         <v>396</v>
@@ -17966,7 +17966,7 @@
         <v>394</v>
       </c>
       <c r="B389" s="12" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C389" s="3" t="s">
         <v>398</v>
@@ -18044,7 +18044,7 @@
         <v>396</v>
       </c>
       <c r="B391" s="12" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C391" s="3" t="s">
         <v>400</v>
@@ -18161,7 +18161,7 @@
         <v>399</v>
       </c>
       <c r="B394" s="12" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C394" s="3" t="s">
         <v>403</v>
@@ -18200,7 +18200,7 @@
         <v>400</v>
       </c>
       <c r="B395" s="12" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C395" s="3" t="s">
         <v>404</v>
@@ -18278,7 +18278,7 @@
         <v>402</v>
       </c>
       <c r="B397" s="12" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C397" s="3" t="s">
         <v>406</v>
@@ -18317,7 +18317,7 @@
         <v>403</v>
       </c>
       <c r="B398" s="12" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C398" s="3" t="s">
         <v>407</v>
@@ -18356,7 +18356,7 @@
         <v>404</v>
       </c>
       <c r="B399" s="12" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C399" s="3" t="s">
         <v>408</v>
@@ -18395,7 +18395,7 @@
         <v>405</v>
       </c>
       <c r="B400" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C400" s="3" t="s">
         <v>409</v>
@@ -18434,10 +18434,10 @@
         <v>406</v>
       </c>
       <c r="B401" s="21" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C401" s="20" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D401" s="3" t="s">
         <v>15</v>
@@ -18473,7 +18473,7 @@
         <v>407</v>
       </c>
       <c r="B402" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C402" s="3" t="s">
         <v>410</v>
@@ -18512,7 +18512,7 @@
         <v>408</v>
       </c>
       <c r="B403" s="12" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C403" s="3" t="s">
         <v>411</v>
@@ -18551,7 +18551,7 @@
         <v>409</v>
       </c>
       <c r="B404" s="12" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C404" s="3" t="s">
         <v>387</v>
@@ -18627,7 +18627,7 @@
         <v>411</v>
       </c>
       <c r="B406" s="12" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C406" s="3" t="s">
         <v>412</v>
@@ -18666,7 +18666,7 @@
         <v>412</v>
       </c>
       <c r="B407" s="12" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C407" s="3" t="s">
         <v>413</v>
@@ -18705,7 +18705,7 @@
         <v>413</v>
       </c>
       <c r="B408" s="12" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C408" s="3" t="s">
         <v>396</v>
@@ -18744,7 +18744,7 @@
         <v>414</v>
       </c>
       <c r="B409" s="12" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C409" s="3" t="s">
         <v>414</v>
@@ -18783,7 +18783,7 @@
         <v>415</v>
       </c>
       <c r="B410" s="12" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C410" s="3" t="s">
         <v>394</v>
@@ -18900,7 +18900,7 @@
         <v>418</v>
       </c>
       <c r="B413" s="12" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C413" s="3" t="s">
         <v>406</v>
@@ -18939,7 +18939,7 @@
         <v>419</v>
       </c>
       <c r="B414" s="12" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C414" s="3" t="s">
         <v>398</v>
@@ -18978,7 +18978,7 @@
         <v>420</v>
       </c>
       <c r="B415" s="12" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C415" s="3" t="s">
         <v>416</v>
@@ -19056,7 +19056,7 @@
         <v>422</v>
       </c>
       <c r="B417" s="12" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C417" s="3" t="s">
         <v>418</v>
@@ -19095,7 +19095,7 @@
         <v>423</v>
       </c>
       <c r="B418" s="12" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C418" s="3" t="s">
         <v>419</v>
@@ -19134,7 +19134,7 @@
         <v>424</v>
       </c>
       <c r="B419" s="12" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C419" s="3" t="s">
         <v>420</v>
@@ -19173,7 +19173,7 @@
         <v>425</v>
       </c>
       <c r="B420" s="12" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C420" s="3" t="s">
         <v>382</v>
@@ -19212,7 +19212,7 @@
         <v>426</v>
       </c>
       <c r="B421" s="12" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C421" s="3" t="s">
         <v>421</v>
@@ -19251,7 +19251,7 @@
         <v>427</v>
       </c>
       <c r="B422" s="12" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C422" s="3" t="s">
         <v>422</v>
@@ -19290,7 +19290,7 @@
         <v>428</v>
       </c>
       <c r="B423" s="6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C423" s="3" t="s">
         <v>423</v>
@@ -19329,7 +19329,7 @@
         <v>429</v>
       </c>
       <c r="B424" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C424" s="3" t="s">
         <v>424</v>
@@ -19446,7 +19446,7 @@
         <v>432</v>
       </c>
       <c r="B427" s="6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C427" s="3" t="s">
         <v>428</v>
@@ -19485,7 +19485,7 @@
         <v>433</v>
       </c>
       <c r="B428" s="12" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C428" s="3" t="s">
         <v>429</v>
@@ -19524,7 +19524,7 @@
         <v>434</v>
       </c>
       <c r="B429" s="12" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C429" s="3" t="s">
         <v>430</v>
@@ -19563,7 +19563,7 @@
         <v>435</v>
       </c>
       <c r="B430" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C430" s="3" t="s">
         <v>431</v>
@@ -19602,7 +19602,7 @@
         <v>436</v>
       </c>
       <c r="B431" s="12" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C431" s="3" t="s">
         <v>432</v>
@@ -19641,7 +19641,7 @@
         <v>437</v>
       </c>
       <c r="B432" s="11" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C432" s="3" t="s">
         <v>433</v>
@@ -19680,7 +19680,7 @@
         <v>438</v>
       </c>
       <c r="B433" s="6" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C433" s="3" t="s">
         <v>434</v>

--- a/data/transactions/أذونات الإضافة لشهر 6.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2302EB-8280-4D5D-A011-368C7DEC7BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B242D7E-7F7E-4D62-8C6D-0DF01DF1F952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2541,7 +2541,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -2591,30 +2591,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF002060"/>
-      </left>
-      <right style="double">
-        <color rgb="FF002060"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF002060"/>
-      </left>
-      <right style="double">
-        <color rgb="FF002060"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color rgb="FF002060"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color indexed="57"/>
       </left>
@@ -2648,7 +2624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2678,37 +2654,37 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2724,19 +2700,13 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -10180,13 +10150,13 @@
         <v>77</v>
       </c>
       <c r="E188" s="29">
-        <v>680</v>
+        <v>94.2</v>
       </c>
       <c r="F188" s="28">
         <v>68.42</v>
       </c>
       <c r="G188" s="29">
-        <v>46525.599999999999</v>
+        <v>6445.16</v>
       </c>
       <c r="H188" s="28">
         <v>709</v>
@@ -10218,11 +10188,15 @@
       <c r="D189" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="E189" s="30"/>
+      <c r="E189" s="29">
+        <v>53</v>
+      </c>
       <c r="F189" s="28">
         <v>68.42</v>
       </c>
-      <c r="G189" s="30"/>
+      <c r="G189" s="29">
+        <v>3626.26</v>
+      </c>
       <c r="H189" s="28">
         <v>709</v>
       </c>
@@ -10253,11 +10227,15 @@
       <c r="D190" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="E190" s="30"/>
+      <c r="E190" s="29">
+        <v>35.299999999999997</v>
+      </c>
       <c r="F190" s="28">
         <v>68.42</v>
       </c>
-      <c r="G190" s="30"/>
+      <c r="G190" s="29">
+        <v>2415.23</v>
+      </c>
       <c r="H190" s="28">
         <v>709</v>
       </c>
@@ -10288,11 +10266,15 @@
       <c r="D191" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="E191" s="30"/>
+      <c r="E191" s="29">
+        <v>94.2</v>
+      </c>
       <c r="F191" s="28">
         <v>68.42</v>
       </c>
-      <c r="G191" s="30"/>
+      <c r="G191" s="29">
+        <v>6445.16</v>
+      </c>
       <c r="H191" s="28">
         <v>709</v>
       </c>
@@ -10323,11 +10305,15 @@
       <c r="D192" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="E192" s="31"/>
+      <c r="E192" s="29">
+        <v>471</v>
+      </c>
       <c r="F192" s="28">
         <v>68.42</v>
       </c>
-      <c r="G192" s="31"/>
+      <c r="G192" s="29">
+        <v>32225.82</v>
+      </c>
       <c r="H192" s="28">
         <v>709</v>
       </c>
@@ -19716,10 +19702,6 @@
     </row>
     <row r="434" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="E188:E192"/>
-    <mergeCell ref="G188:G192"/>
-  </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/transactions/أذونات الإضافة لشهر 6.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28BE414-C230-4037-AC7A-FDDA71FDBAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73577F5-9D5C-4586-93DA-E5BB8AE117DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$432</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$436</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="806">
   <si>
     <t>بورسعيد لصناعة المعادن</t>
   </si>
@@ -2437,6 +2437,24 @@
   </si>
   <si>
     <t>11404012</t>
+  </si>
+  <si>
+    <t>بروفيل باب تلاجة PVC موديل A141</t>
+  </si>
+  <si>
+    <t>19/4/2026</t>
+  </si>
+  <si>
+    <t>سماريل</t>
+  </si>
+  <si>
+    <t>بروفيل باب تلاجة PVC موديل A142</t>
+  </si>
+  <si>
+    <t>بروفيل باب تلاجة PVC موديل A143</t>
+  </si>
+  <si>
+    <t>بروفيل باب تلاجة PVC موديل A144</t>
   </si>
 </sst>
 </file>
@@ -2633,7 +2651,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2716,6 +2734,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2998,7 +3031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M433"/>
+  <dimension ref="A1:M438"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" customWidth="1"/>
@@ -19657,8 +19690,8 @@
       <c r="H432" s="3">
         <v>4665</v>
       </c>
-      <c r="I432" s="7" t="s">
-        <v>435</v>
+      <c r="I432" s="7">
+        <v>46086</v>
       </c>
       <c r="J432" s="3"/>
       <c r="K432" s="3" t="s">
@@ -19671,7 +19704,174 @@
         <v>427</v>
       </c>
     </row>
-    <row r="433" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="433" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A433" s="5">
+        <v>439</v>
+      </c>
+      <c r="B433" s="30"/>
+      <c r="C433" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="D433" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E433" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F433" s="3">
+        <v>90.957490000000007</v>
+      </c>
+      <c r="G433" s="3">
+        <f>F433*E433</f>
+        <v>90957.49</v>
+      </c>
+      <c r="H433" s="3">
+        <v>38</v>
+      </c>
+      <c r="I433" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="J433" s="3"/>
+      <c r="K433" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="L433" s="3">
+        <v>6454</v>
+      </c>
+      <c r="M433" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="434" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A434" s="5">
+        <v>440</v>
+      </c>
+      <c r="B434" s="30"/>
+      <c r="C434" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="D434" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E434" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F434" s="3">
+        <v>159.40960000000001</v>
+      </c>
+      <c r="G434" s="3">
+        <f t="shared" ref="G434:G436" si="0">F434*E434</f>
+        <v>159409.60000000001</v>
+      </c>
+      <c r="H434" s="3">
+        <v>38</v>
+      </c>
+      <c r="I434" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="J434" s="3"/>
+      <c r="K434" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="L434" s="3">
+        <v>6454</v>
+      </c>
+      <c r="M434" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="435" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A435" s="5">
+        <v>441</v>
+      </c>
+      <c r="B435" s="30"/>
+      <c r="C435" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="D435" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E435" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F435" s="3">
+        <v>135.96741</v>
+      </c>
+      <c r="G435" s="3">
+        <f t="shared" si="0"/>
+        <v>135967.41</v>
+      </c>
+      <c r="H435" s="3">
+        <v>38</v>
+      </c>
+      <c r="I435" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="J435" s="3"/>
+      <c r="K435" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="L435" s="3">
+        <v>6454</v>
+      </c>
+      <c r="M435" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="436" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A436" s="5">
+        <v>442</v>
+      </c>
+      <c r="B436" s="30"/>
+      <c r="C436" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="D436" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E436" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F436" s="3">
+        <v>145.3443</v>
+      </c>
+      <c r="G436" s="3">
+        <f t="shared" si="0"/>
+        <v>145344.30000000002</v>
+      </c>
+      <c r="H436" s="3">
+        <v>38</v>
+      </c>
+      <c r="I436" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="J436" s="3"/>
+      <c r="K436" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="L436" s="3">
+        <v>6454</v>
+      </c>
+      <c r="M436" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="437" spans="1:13" ht="28.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="438" spans="1:13" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A438" s="31"/>
+      <c r="B438" s="32"/>
+      <c r="C438" s="33"/>
+      <c r="D438" s="33"/>
+      <c r="E438" s="33"/>
+      <c r="F438" s="33"/>
+      <c r="G438" s="33"/>
+      <c r="H438" s="33"/>
+      <c r="I438" s="34"/>
+      <c r="J438" s="33"/>
+      <c r="K438" s="33"/>
+      <c r="L438" s="33"/>
+      <c r="M438" s="34"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
